--- a/public/templates/LembagaKonsultasi.xlsx
+++ b/public/templates/LembagaKonsultasi.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0dccc67157c6ef23/文档/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECT WEB RANDIKA\sipandakabulan-new\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6CE8C7E4-E63C-4C26-9959-10DDC12AE891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41DBA408-AB39-43D1-9338-E5868D265266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{07846A05-06D5-4E51-B0BC-AA666ECD7F2B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{07846A05-06D5-4E51-B0BC-AA666ECD7F2B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -169,15 +167,15 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -516,9 +514,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE494813-D636-45BF-B4AE-0E530DCDFEBB}">
   <dimension ref="B3:Q11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="3" spans="2:17" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>0</v>
       </c>
@@ -533,16 +531,16 @@
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="4"/>
-      <c r="Q3" s="4"/>
-    </row>
-    <row r="4" spans="2:17" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+    </row>
+    <row r="4" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -554,17 +552,17 @@
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
       <c r="L4" s="3">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
       <c r="O4" s="3">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
     </row>
-    <row r="5" spans="2:17" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -579,14 +577,14 @@
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="6"/>
-      <c r="Q5" s="6"/>
-    </row>
-    <row r="6" spans="2:17" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4"/>
+    </row>
+    <row r="6" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
         <v>2</v>
       </c>
@@ -601,14 +599,14 @@
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="6"/>
-      <c r="Q6" s="6"/>
-    </row>
-    <row r="7" spans="2:17" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="4"/>
+    </row>
+    <row r="7" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
         <v>3</v>
       </c>
@@ -623,14 +621,14 @@
       <c r="I7" s="5"/>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="6"/>
-    </row>
-    <row r="8" spans="2:17" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4"/>
+    </row>
+    <row r="8" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B8" s="2">
         <v>4</v>
       </c>
@@ -645,14 +643,14 @@
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
-      <c r="Q8" s="6"/>
-    </row>
-    <row r="9" spans="2:17" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="4"/>
+      <c r="P8" s="4"/>
+      <c r="Q8" s="4"/>
+    </row>
+    <row r="9" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B9" s="2">
         <v>5</v>
       </c>
@@ -667,14 +665,14 @@
       <c r="I9" s="5"/>
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6"/>
-      <c r="Q9" s="6"/>
-    </row>
-    <row r="10" spans="2:17" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
+      <c r="O9" s="4"/>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="4"/>
+    </row>
+    <row r="10" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B10" s="2">
         <v>6</v>
       </c>
@@ -689,14 +687,14 @@
       <c r="I10" s="5"/>
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="6"/>
-      <c r="O10" s="6"/>
-      <c r="P10" s="6"/>
-      <c r="Q10" s="6"/>
-    </row>
-    <row r="11" spans="2:17" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
+      <c r="O10" s="4"/>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="4"/>
+    </row>
+    <row r="11" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B11" s="1">
         <v>7</v>
       </c>
@@ -711,15 +709,25 @@
       <c r="I11" s="5"/>
       <c r="J11" s="5"/>
       <c r="K11" s="5"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="6"/>
-      <c r="O11" s="6"/>
-      <c r="P11" s="6"/>
-      <c r="Q11" s="6"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="O5:Q5"/>
+    <mergeCell ref="O6:Q6"/>
+    <mergeCell ref="O7:Q7"/>
+    <mergeCell ref="C3:K4"/>
+    <mergeCell ref="C5:K5"/>
+    <mergeCell ref="C6:K6"/>
+    <mergeCell ref="C7:K7"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="L7:N7"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="O8:Q8"/>
     <mergeCell ref="O9:Q9"/>
@@ -736,16 +744,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="L3:Q3"/>
-    <mergeCell ref="C3:K4"/>
-    <mergeCell ref="C5:K5"/>
-    <mergeCell ref="C6:K6"/>
-    <mergeCell ref="C7:K7"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="O5:Q5"/>
-    <mergeCell ref="O6:Q6"/>
-    <mergeCell ref="O7:Q7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
